--- a/excel/finanzas-master.xlsx
+++ b/excel/finanzas-master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\japaricio\Dropbox\Cuentas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9C9C46F-CF51-414E-9808-955EF8381181}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43B95C45-7580-4E0C-89BF-299D49EDD000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MASTER" sheetId="1" r:id="rId1"/>
@@ -924,7 +924,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1015,6 +1015,9 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2830,7 +2833,7 @@
     <tabColor rgb="FF0F766E"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K55"/>
+  <dimension ref="A1:L55"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="28" style="2" customWidth="1"/>
@@ -2846,7 +2849,7 @@
     <col min="12" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2880,9 +2883,12 @@
       <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" ht="4.95" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="3" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L1" s="31">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="4.95" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="25" t="s">
         <v>11</v>
       </c>
@@ -2897,7 +2903,7 @@
       <c r="J3" s="25"/>
       <c r="K3" s="25"/>
     </row>
-    <row r="4" spans="1:11" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="13" t="s">
         <v>12</v>
       </c>
@@ -2911,7 +2917,8 @@
         <v>15</v>
       </c>
       <c r="E4" s="5">
-        <v>2330</v>
+        <f>MASTER!E4-MASTER!E4*$L$1</f>
+        <v>1165</v>
       </c>
       <c r="F4" s="15">
         <v>2026</v>
@@ -2930,7 +2937,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="14" t="s">
         <v>23</v>
       </c>
@@ -2943,8 +2950,9 @@
       <c r="D5" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="E5" s="7">
-        <v>2538</v>
+      <c r="E5" s="5">
+        <f>MASTER!E5-MASTER!E5*$L$1</f>
+        <v>1269</v>
       </c>
       <c r="F5" s="18">
         <v>2026</v>
@@ -2965,7 +2973,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="13" t="s">
         <v>18</v>
       </c>
@@ -2979,7 +2987,8 @@
         <v>20</v>
       </c>
       <c r="E6" s="5">
-        <v>1450</v>
+        <f>MASTER!E6-MASTER!E6*$L$1</f>
+        <v>725</v>
       </c>
       <c r="F6" s="15">
         <v>2026</v>
@@ -3000,9 +3009,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="9" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="8" spans="1:11" ht="9" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="9" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" ht="9" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="8" spans="1:12" ht="9" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="9" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="26" t="s">
         <v>26</v>
       </c>
@@ -3017,7 +3026,7 @@
       <c r="J9" s="26"/>
       <c r="K9" s="26"/>
     </row>
-    <row r="10" spans="1:11" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="13" t="s">
         <v>40</v>
       </c>
@@ -3031,7 +3040,8 @@
         <v>41</v>
       </c>
       <c r="E10" s="5">
-        <v>1350</v>
+        <f>MASTER!E10-MASTER!E10*$L$1</f>
+        <v>675</v>
       </c>
       <c r="F10" s="15">
         <v>2026</v>
@@ -3050,7 +3060,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="14" t="s">
         <v>125</v>
       </c>
@@ -3063,7 +3073,8 @@
       <c r="D11" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="E11" s="7">
+      <c r="E11" s="5">
+        <f>MASTER!E11-MASTER!E11*$L$1</f>
         <v>0</v>
       </c>
       <c r="F11" s="18">
@@ -3083,7 +3094,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="7.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" ht="7.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="21"/>
       <c r="B12" s="21"/>
       <c r="C12" s="21"/>
@@ -3096,7 +3107,7 @@
       <c r="J12" s="22"/>
       <c r="K12" s="22"/>
     </row>
-    <row r="13" spans="1:11" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="13" t="s">
         <v>37</v>
       </c>
@@ -3110,7 +3121,8 @@
         <v>38</v>
       </c>
       <c r="E13" s="5">
-        <v>35</v>
+        <f>MASTER!E13-MASTER!E13*$L$1</f>
+        <v>17.5</v>
       </c>
       <c r="F13" s="15">
         <v>2026</v>
@@ -3131,7 +3143,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="14" t="s">
         <v>35</v>
       </c>
@@ -3144,8 +3156,9 @@
       <c r="D14" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="E14" s="7">
-        <v>50</v>
+      <c r="E14" s="5">
+        <f>MASTER!E14-MASTER!E14*$L$1</f>
+        <v>25</v>
       </c>
       <c r="F14" s="18">
         <v>2026</v>
@@ -3164,7 +3177,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="13" t="s">
         <v>127</v>
       </c>
@@ -3178,7 +3191,8 @@
         <v>128</v>
       </c>
       <c r="E15" s="5">
-        <v>65</v>
+        <f>MASTER!E15-MASTER!E15*$L$1</f>
+        <v>32.5</v>
       </c>
       <c r="F15" s="15">
         <v>2026</v>
@@ -3199,7 +3213,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="14" t="s">
         <v>33</v>
       </c>
@@ -3212,8 +3226,9 @@
       <c r="D16" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="E16" s="7">
-        <v>14</v>
+      <c r="E16" s="5">
+        <f>MASTER!E16-MASTER!E16*$L$1</f>
+        <v>7</v>
       </c>
       <c r="F16" s="18">
         <v>2026</v>
@@ -3259,7 +3274,8 @@
         <v>30</v>
       </c>
       <c r="E18" s="5">
-        <v>80</v>
+        <f>MASTER!E18-MASTER!E18*$L$1</f>
+        <v>40</v>
       </c>
       <c r="F18" s="15">
         <v>2026</v>
@@ -3291,8 +3307,9 @@
       <c r="D19" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="E19" s="7">
-        <v>34</v>
+      <c r="E19" s="5">
+        <f>MASTER!E19-MASTER!E19*$L$1</f>
+        <v>17</v>
       </c>
       <c r="F19" s="18">
         <v>2026</v>
@@ -3338,7 +3355,8 @@
         <v>71</v>
       </c>
       <c r="E21" s="5">
-        <v>50</v>
+        <f>MASTER!E21-MASTER!E21*$L$1</f>
+        <v>25</v>
       </c>
       <c r="F21" s="15">
         <v>2026</v>
@@ -3370,8 +3388,9 @@
       <c r="D22" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="E22" s="7">
-        <v>50</v>
+      <c r="E22" s="5">
+        <f>MASTER!E22-MASTER!E22*$L$1</f>
+        <v>25</v>
       </c>
       <c r="F22" s="18">
         <v>2026</v>
@@ -3404,7 +3423,8 @@
         <v>77</v>
       </c>
       <c r="E23" s="5">
-        <v>25</v>
+        <f>MASTER!E23-MASTER!E23*$L$1</f>
+        <v>12.5</v>
       </c>
       <c r="F23" s="15">
         <v>2026</v>
@@ -3436,8 +3456,9 @@
       <c r="D24" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="E24" s="7">
-        <v>15</v>
+      <c r="E24" s="5">
+        <f>MASTER!E24-MASTER!E24*$L$1</f>
+        <v>7.5</v>
       </c>
       <c r="F24" s="18">
         <v>2026</v>
@@ -3470,7 +3491,8 @@
         <v>83</v>
       </c>
       <c r="E25" s="5">
-        <v>20</v>
+        <f>MASTER!E25-MASTER!E25*$L$1</f>
+        <v>10</v>
       </c>
       <c r="F25" s="15">
         <v>2026</v>
@@ -3502,8 +3524,9 @@
       <c r="D26" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="E26" s="7">
-        <v>50</v>
+      <c r="E26" s="5">
+        <f>MASTER!E26-MASTER!E26*$L$1</f>
+        <v>25</v>
       </c>
       <c r="F26" s="18">
         <v>2026</v>
@@ -3536,7 +3559,8 @@
         <v>49</v>
       </c>
       <c r="E27" s="5">
-        <v>30</v>
+        <f>MASTER!E27-MASTER!E27*$L$1</f>
+        <v>15</v>
       </c>
       <c r="F27" s="15">
         <v>2026</v>
@@ -3570,8 +3594,9 @@
       <c r="D28" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="E28" s="7">
-        <v>1</v>
+      <c r="E28" s="5">
+        <f>MASTER!E28-MASTER!E28*$L$1</f>
+        <v>0.5</v>
       </c>
       <c r="F28" s="18">
         <v>2026</v>
@@ -3604,7 +3629,8 @@
         <v>61</v>
       </c>
       <c r="E29" s="5">
-        <v>120</v>
+        <f>MASTER!E29-MASTER!E29*$L$1</f>
+        <v>60</v>
       </c>
       <c r="F29" s="15">
         <v>2026</v>
@@ -3652,7 +3678,8 @@
         <v>43</v>
       </c>
       <c r="E31" s="5">
-        <v>55</v>
+        <f>MASTER!E31-MASTER!E31*$L$1</f>
+        <v>27.5</v>
       </c>
       <c r="F31" s="15">
         <v>2026</v>
@@ -3684,8 +3711,9 @@
       <c r="D32" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="E32" s="7">
-        <v>38</v>
+      <c r="E32" s="5">
+        <f>MASTER!E32-MASTER!E32*$L$1</f>
+        <v>19</v>
       </c>
       <c r="F32" s="18">
         <v>2026</v>
@@ -3733,7 +3761,8 @@
         <v>64</v>
       </c>
       <c r="E34" s="5">
-        <v>350</v>
+        <f>MASTER!E34-MASTER!E34*$L$1</f>
+        <v>175</v>
       </c>
       <c r="F34" s="15">
         <v>2026</v>
@@ -3767,8 +3796,9 @@
       <c r="D35" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="E35" s="7">
-        <v>350</v>
+      <c r="E35" s="5">
+        <f>MASTER!E35-MASTER!E35*$L$1</f>
+        <v>175</v>
       </c>
       <c r="F35" s="18">
         <v>2026</v>
@@ -3803,7 +3833,8 @@
         <v>69</v>
       </c>
       <c r="E36" s="5">
-        <v>100</v>
+        <f>MASTER!E36-MASTER!E36*$L$1</f>
+        <v>50</v>
       </c>
       <c r="F36" s="15">
         <v>2026</v>
@@ -3837,8 +3868,9 @@
       <c r="D37" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="E37" s="7">
-        <v>70</v>
+      <c r="E37" s="5">
+        <f>MASTER!E37-MASTER!E37*$L$1</f>
+        <v>35</v>
       </c>
       <c r="F37" s="18">
         <v>2026</v>
@@ -3884,7 +3916,8 @@
         <v>53</v>
       </c>
       <c r="E39" s="5">
-        <v>42</v>
+        <f>MASTER!E39-MASTER!E39*$L$1</f>
+        <v>21</v>
       </c>
       <c r="F39" s="15">
         <v>2026</v>
@@ -3918,8 +3951,9 @@
       <c r="D40" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="E40" s="7">
-        <v>15</v>
+      <c r="E40" s="5">
+        <f>MASTER!E40-MASTER!E40*$L$1</f>
+        <v>7.5</v>
       </c>
       <c r="F40" s="18">
         <v>2026</v>
@@ -3954,7 +3988,8 @@
         <v>55</v>
       </c>
       <c r="E41" s="5">
-        <v>55</v>
+        <f>MASTER!E41-MASTER!E41*$L$1</f>
+        <v>27.5</v>
       </c>
       <c r="F41" s="15">
         <v>2026</v>
@@ -4002,7 +4037,8 @@
         <v>85</v>
       </c>
       <c r="E43" s="5">
-        <v>50</v>
+        <f>MASTER!E43-MASTER!E43*$L$1</f>
+        <v>25</v>
       </c>
       <c r="F43" s="15">
         <v>2026</v>
@@ -4036,8 +4072,9 @@
       <c r="D44" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="E44" s="7">
-        <v>200</v>
+      <c r="E44" s="5">
+        <f>MASTER!E44-MASTER!E44*$L$1</f>
+        <v>100</v>
       </c>
       <c r="F44" s="18">
         <v>2026</v>
@@ -4091,7 +4128,8 @@
         <v>92</v>
       </c>
       <c r="E48" s="5">
-        <v>800</v>
+        <f>MASTER!E48-MASTER!E48*$L$1</f>
+        <v>400</v>
       </c>
       <c r="F48" s="15">
         <v>2026</v>
@@ -4125,8 +4163,9 @@
       <c r="D49" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="E49" s="7">
-        <v>900</v>
+      <c r="E49" s="5">
+        <f>MASTER!E49-MASTER!E49*$L$1</f>
+        <v>450</v>
       </c>
       <c r="F49" s="18">
         <v>2026</v>
@@ -4161,7 +4200,8 @@
         <v>98</v>
       </c>
       <c r="E50" s="5">
-        <v>2000</v>
+        <f>MASTER!E50-MASTER!E50*$L$1</f>
+        <v>1000</v>
       </c>
       <c r="F50" s="15">
         <v>2026</v>
@@ -4195,8 +4235,9 @@
       <c r="D51" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="E51" s="7">
-        <v>1400</v>
+      <c r="E51" s="5">
+        <f>MASTER!E51-MASTER!E51*$L$1</f>
+        <v>700</v>
       </c>
       <c r="F51" s="18">
         <v>2026</v>
@@ -4231,7 +4272,8 @@
         <v>103</v>
       </c>
       <c r="E52" s="5">
-        <v>400</v>
+        <f>MASTER!E52-MASTER!E52*$L$1</f>
+        <v>200</v>
       </c>
       <c r="F52" s="15">
         <v>2026</v>
@@ -4267,7 +4309,7 @@
     <mergeCell ref="A9:K9"/>
     <mergeCell ref="A47:K47"/>
   </mergeCells>
-  <conditionalFormatting sqref="A2:K2 A3 A4:K8 A9 A10:K46 A47 A48:K509">
+  <conditionalFormatting sqref="A2:K2 A3 A9 A47 A4:K8 A10:K46 A48:K509">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>AND($A2&lt;&gt;"",$B2&lt;&gt;"",$J2=0)</formula>
     </cfRule>

--- a/excel/finanzas-master.xlsx
+++ b/excel/finanzas-master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\japaricio\Dropbox\Cuentas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43B95C45-7580-4E0C-89BF-299D49EDD000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{319137BD-64B9-4EE4-B38A-01684D6B0BA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -998,6 +998,9 @@
     <xf numFmtId="0" fontId="9" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1015,9 +1018,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1407,19 +1407,19 @@
     </row>
     <row r="2" spans="1:11" ht="4.95" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="25" t="s">
+      <c r="A3" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="25"/>
-      <c r="C3" s="25"/>
-      <c r="D3" s="25"/>
-      <c r="E3" s="25"/>
-      <c r="F3" s="25"/>
-      <c r="G3" s="25"/>
-      <c r="H3" s="25"/>
-      <c r="I3" s="25"/>
-      <c r="J3" s="25"/>
-      <c r="K3" s="25"/>
+      <c r="B3" s="26"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="26"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="26"/>
+      <c r="G3" s="26"/>
+      <c r="H3" s="26"/>
+      <c r="I3" s="26"/>
+      <c r="J3" s="26"/>
+      <c r="K3" s="26"/>
     </row>
     <row r="4" spans="1:11" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="13" t="s">
@@ -1527,19 +1527,19 @@
     <row r="7" spans="1:11" ht="9" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="8" spans="1:11" ht="9" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="9" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="26" t="s">
+      <c r="A9" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="26"/>
-      <c r="C9" s="26"/>
-      <c r="D9" s="26"/>
-      <c r="E9" s="26"/>
-      <c r="F9" s="26"/>
-      <c r="G9" s="26"/>
-      <c r="H9" s="26"/>
-      <c r="I9" s="26"/>
-      <c r="J9" s="26"/>
-      <c r="K9" s="26"/>
+      <c r="B9" s="27"/>
+      <c r="C9" s="27"/>
+      <c r="D9" s="27"/>
+      <c r="E9" s="27"/>
+      <c r="F9" s="27"/>
+      <c r="G9" s="27"/>
+      <c r="H9" s="27"/>
+      <c r="I9" s="27"/>
+      <c r="J9" s="27"/>
+      <c r="K9" s="27"/>
     </row>
     <row r="10" spans="1:11" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="13" t="s">
@@ -2587,19 +2587,19 @@
     </row>
     <row r="46" spans="1:11" ht="9" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="47" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="27" t="s">
+      <c r="A47" s="28" t="s">
         <v>89</v>
       </c>
-      <c r="B47" s="27"/>
-      <c r="C47" s="27"/>
-      <c r="D47" s="27"/>
-      <c r="E47" s="27"/>
-      <c r="F47" s="27"/>
-      <c r="G47" s="27"/>
-      <c r="H47" s="27"/>
-      <c r="I47" s="27"/>
-      <c r="J47" s="27"/>
-      <c r="K47" s="27"/>
+      <c r="B47" s="28"/>
+      <c r="C47" s="28"/>
+      <c r="D47" s="28"/>
+      <c r="E47" s="28"/>
+      <c r="F47" s="28"/>
+      <c r="G47" s="28"/>
+      <c r="H47" s="28"/>
+      <c r="I47" s="28"/>
+      <c r="J47" s="28"/>
+      <c r="K47" s="28"/>
     </row>
     <row r="48" spans="1:11" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="13" t="s">
@@ -2833,7 +2833,7 @@
     <tabColor rgb="FF0F766E"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L55"/>
+  <dimension ref="A1:L59"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="28" style="2" customWidth="1"/>
@@ -2883,25 +2883,25 @@
       <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="31">
-        <v>0.5</v>
+      <c r="L1" s="25">
+        <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="4.95" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="25" t="s">
+      <c r="A3" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="25"/>
-      <c r="C3" s="25"/>
-      <c r="D3" s="25"/>
-      <c r="E3" s="25"/>
-      <c r="F3" s="25"/>
-      <c r="G3" s="25"/>
-      <c r="H3" s="25"/>
-      <c r="I3" s="25"/>
-      <c r="J3" s="25"/>
-      <c r="K3" s="25"/>
+      <c r="B3" s="26"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="26"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="26"/>
+      <c r="G3" s="26"/>
+      <c r="H3" s="26"/>
+      <c r="I3" s="26"/>
+      <c r="J3" s="26"/>
+      <c r="K3" s="26"/>
     </row>
     <row r="4" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="13" t="s">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="E4" s="5">
         <f>MASTER!E4-MASTER!E4*$L$1</f>
-        <v>1165</v>
+        <v>0</v>
       </c>
       <c r="F4" s="15">
         <v>2026</v>
@@ -2952,7 +2952,7 @@
       </c>
       <c r="E5" s="5">
         <f>MASTER!E5-MASTER!E5*$L$1</f>
-        <v>1269</v>
+        <v>0</v>
       </c>
       <c r="F5" s="18">
         <v>2026</v>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="E6" s="5">
         <f>MASTER!E6-MASTER!E6*$L$1</f>
-        <v>725</v>
+        <v>0</v>
       </c>
       <c r="F6" s="15">
         <v>2026</v>
@@ -3012,19 +3012,22 @@
     <row r="7" spans="1:12" ht="9" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="8" spans="1:12" ht="9" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="9" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="26" t="s">
+      <c r="A9" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="26"/>
-      <c r="C9" s="26"/>
-      <c r="D9" s="26"/>
-      <c r="E9" s="26"/>
-      <c r="F9" s="26"/>
-      <c r="G9" s="26"/>
-      <c r="H9" s="26"/>
-      <c r="I9" s="26"/>
-      <c r="J9" s="26"/>
-      <c r="K9" s="26"/>
+      <c r="B9" s="27"/>
+      <c r="C9" s="27"/>
+      <c r="D9" s="27"/>
+      <c r="E9" s="27"/>
+      <c r="F9" s="27"/>
+      <c r="G9" s="27"/>
+      <c r="H9" s="27"/>
+      <c r="I9" s="27"/>
+      <c r="J9" s="27"/>
+      <c r="K9" s="27"/>
+      <c r="L9" s="25">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="10" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="13" t="s">
@@ -3040,8 +3043,8 @@
         <v>41</v>
       </c>
       <c r="E10" s="5">
-        <f>MASTER!E10-MASTER!E10*$L$1</f>
-        <v>675</v>
+        <f>MASTER!E10-MASTER!E10*$L$9</f>
+        <v>810</v>
       </c>
       <c r="F10" s="15">
         <v>2026</v>
@@ -3074,7 +3077,7 @@
         <v>126</v>
       </c>
       <c r="E11" s="5">
-        <f>MASTER!E11-MASTER!E11*$L$1</f>
+        <f>MASTER!E11-MASTER!E11*$L$9</f>
         <v>0</v>
       </c>
       <c r="F11" s="18">
@@ -3121,8 +3124,8 @@
         <v>38</v>
       </c>
       <c r="E13" s="5">
-        <f>MASTER!E13-MASTER!E13*$L$1</f>
-        <v>17.5</v>
+        <f>MASTER!E13-MASTER!E13*$L$9</f>
+        <v>21</v>
       </c>
       <c r="F13" s="15">
         <v>2026</v>
@@ -3157,8 +3160,8 @@
         <v>36</v>
       </c>
       <c r="E14" s="5">
-        <f>MASTER!E14-MASTER!E14*$L$1</f>
-        <v>25</v>
+        <f>MASTER!E14-MASTER!E14*$L$9</f>
+        <v>30</v>
       </c>
       <c r="F14" s="18">
         <v>2026</v>
@@ -3191,8 +3194,8 @@
         <v>128</v>
       </c>
       <c r="E15" s="5">
-        <f>MASTER!E15-MASTER!E15*$L$1</f>
-        <v>32.5</v>
+        <f>MASTER!E15-MASTER!E15*$L$9</f>
+        <v>39</v>
       </c>
       <c r="F15" s="15">
         <v>2026</v>
@@ -3227,8 +3230,8 @@
         <v>34</v>
       </c>
       <c r="E16" s="5">
-        <f>MASTER!E16-MASTER!E16*$L$1</f>
-        <v>7</v>
+        <f>MASTER!E16-MASTER!E16*$L$9</f>
+        <v>8.3999999999999986</v>
       </c>
       <c r="F16" s="18">
         <v>2026</v>
@@ -3274,8 +3277,8 @@
         <v>30</v>
       </c>
       <c r="E18" s="5">
-        <f>MASTER!E18-MASTER!E18*$L$1</f>
-        <v>40</v>
+        <f>MASTER!E18-MASTER!E18*$L$9</f>
+        <v>48</v>
       </c>
       <c r="F18" s="15">
         <v>2026</v>
@@ -3308,8 +3311,8 @@
         <v>32</v>
       </c>
       <c r="E19" s="5">
-        <f>MASTER!E19-MASTER!E19*$L$1</f>
-        <v>17</v>
+        <f>MASTER!E19-MASTER!E19*$L$9</f>
+        <v>20.399999999999999</v>
       </c>
       <c r="F19" s="18">
         <v>2026</v>
@@ -3355,8 +3358,8 @@
         <v>71</v>
       </c>
       <c r="E21" s="5">
-        <f>MASTER!E21-MASTER!E21*$L$1</f>
-        <v>25</v>
+        <f>MASTER!E21-MASTER!E21*$L$9</f>
+        <v>30</v>
       </c>
       <c r="F21" s="15">
         <v>2026</v>
@@ -3389,8 +3392,8 @@
         <v>73</v>
       </c>
       <c r="E22" s="5">
-        <f>MASTER!E22-MASTER!E22*$L$1</f>
-        <v>25</v>
+        <f>MASTER!E22-MASTER!E22*$L$9</f>
+        <v>30</v>
       </c>
       <c r="F22" s="18">
         <v>2026</v>
@@ -3423,8 +3426,8 @@
         <v>77</v>
       </c>
       <c r="E23" s="5">
-        <f>MASTER!E23-MASTER!E23*$L$1</f>
-        <v>12.5</v>
+        <f>MASTER!E23-MASTER!E23*$L$9</f>
+        <v>15</v>
       </c>
       <c r="F23" s="15">
         <v>2026</v>
@@ -3457,8 +3460,8 @@
         <v>79</v>
       </c>
       <c r="E24" s="5">
-        <f>MASTER!E24-MASTER!E24*$L$1</f>
-        <v>7.5</v>
+        <f>MASTER!E24-MASTER!E24*$L$9</f>
+        <v>9</v>
       </c>
       <c r="F24" s="18">
         <v>2026</v>
@@ -3491,8 +3494,8 @@
         <v>83</v>
       </c>
       <c r="E25" s="5">
-        <f>MASTER!E25-MASTER!E25*$L$1</f>
-        <v>10</v>
+        <f>MASTER!E25-MASTER!E25*$L$9</f>
+        <v>12</v>
       </c>
       <c r="F25" s="15">
         <v>2026</v>
@@ -3525,8 +3528,8 @@
         <v>75</v>
       </c>
       <c r="E26" s="5">
-        <f>MASTER!E26-MASTER!E26*$L$1</f>
-        <v>25</v>
+        <f>MASTER!E26-MASTER!E26*$L$9</f>
+        <v>30</v>
       </c>
       <c r="F26" s="18">
         <v>2026</v>
@@ -3559,8 +3562,8 @@
         <v>49</v>
       </c>
       <c r="E27" s="5">
-        <f>MASTER!E27-MASTER!E27*$L$1</f>
-        <v>15</v>
+        <f>MASTER!E27-MASTER!E27*$L$9</f>
+        <v>18</v>
       </c>
       <c r="F27" s="15">
         <v>2026</v>
@@ -3595,8 +3598,8 @@
         <v>49</v>
       </c>
       <c r="E28" s="5">
-        <f>MASTER!E28-MASTER!E28*$L$1</f>
-        <v>0.5</v>
+        <f>MASTER!E28-MASTER!E28*$L$9</f>
+        <v>0.6</v>
       </c>
       <c r="F28" s="18">
         <v>2026</v>
@@ -3629,8 +3632,8 @@
         <v>61</v>
       </c>
       <c r="E29" s="5">
-        <f>MASTER!E29-MASTER!E29*$L$1</f>
-        <v>60</v>
+        <f>MASTER!E29-MASTER!E29*$L$9</f>
+        <v>72</v>
       </c>
       <c r="F29" s="15">
         <v>2026</v>
@@ -3678,8 +3681,8 @@
         <v>43</v>
       </c>
       <c r="E31" s="5">
-        <f>MASTER!E31-MASTER!E31*$L$1</f>
-        <v>27.5</v>
+        <f>MASTER!E31-MASTER!E31*$L$9</f>
+        <v>33</v>
       </c>
       <c r="F31" s="15">
         <v>2026</v>
@@ -3712,8 +3715,8 @@
         <v>46</v>
       </c>
       <c r="E32" s="5">
-        <f>MASTER!E32-MASTER!E32*$L$1</f>
-        <v>19</v>
+        <f>MASTER!E32-MASTER!E32*$L$9</f>
+        <v>22.799999999999997</v>
       </c>
       <c r="F32" s="18">
         <v>2026</v>
@@ -3734,7 +3737,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="33" spans="1:11" ht="7.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:12" ht="7.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="21"/>
       <c r="B33" s="21"/>
       <c r="C33" s="21"/>
@@ -3747,7 +3750,7 @@
       <c r="J33" s="22"/>
       <c r="K33" s="22"/>
     </row>
-    <row r="34" spans="1:11" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="13" t="s">
         <v>63</v>
       </c>
@@ -3761,8 +3764,8 @@
         <v>64</v>
       </c>
       <c r="E34" s="5">
-        <f>MASTER!E34-MASTER!E34*$L$1</f>
-        <v>175</v>
+        <f>MASTER!E34-MASTER!E34*$L$9</f>
+        <v>210</v>
       </c>
       <c r="F34" s="15">
         <v>2026</v>
@@ -3783,7 +3786,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="35" spans="1:11" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="14" t="s">
         <v>65</v>
       </c>
@@ -3797,8 +3800,8 @@
         <v>66</v>
       </c>
       <c r="E35" s="5">
-        <f>MASTER!E35-MASTER!E35*$L$1</f>
-        <v>175</v>
+        <f>MASTER!E35-MASTER!E35*$L$9</f>
+        <v>210</v>
       </c>
       <c r="F35" s="18">
         <v>2026</v>
@@ -3819,7 +3822,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="36" spans="1:11" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="13" t="s">
         <v>68</v>
       </c>
@@ -3833,8 +3836,8 @@
         <v>69</v>
       </c>
       <c r="E36" s="5">
-        <f>MASTER!E36-MASTER!E36*$L$1</f>
-        <v>50</v>
+        <f>MASTER!E36-MASTER!E36*$L$9</f>
+        <v>60</v>
       </c>
       <c r="F36" s="15">
         <v>2026</v>
@@ -3855,7 +3858,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="37" spans="1:11" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="14" t="s">
         <v>80</v>
       </c>
@@ -3869,8 +3872,8 @@
         <v>81</v>
       </c>
       <c r="E37" s="5">
-        <f>MASTER!E37-MASTER!E37*$L$1</f>
-        <v>35</v>
+        <f>MASTER!E37-MASTER!E37*$L$9</f>
+        <v>42</v>
       </c>
       <c r="F37" s="18">
         <v>2026</v>
@@ -3889,7 +3892,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="38" spans="1:11" ht="7.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:12" ht="7.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="21"/>
       <c r="B38" s="21"/>
       <c r="C38" s="21"/>
@@ -3902,7 +3905,7 @@
       <c r="J38" s="22"/>
       <c r="K38" s="22"/>
     </row>
-    <row r="39" spans="1:11" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="13" t="s">
         <v>52</v>
       </c>
@@ -3916,8 +3919,8 @@
         <v>53</v>
       </c>
       <c r="E39" s="5">
-        <f>MASTER!E39-MASTER!E39*$L$1</f>
-        <v>21</v>
+        <f>MASTER!E39-MASTER!E39*$L$9</f>
+        <v>25.2</v>
       </c>
       <c r="F39" s="15">
         <v>2026</v>
@@ -3938,7 +3941,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="40" spans="1:11" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="14" t="s">
         <v>57</v>
       </c>
@@ -3952,8 +3955,8 @@
         <v>58</v>
       </c>
       <c r="E40" s="5">
-        <f>MASTER!E40-MASTER!E40*$L$1</f>
-        <v>7.5</v>
+        <f>MASTER!E40-MASTER!E40*$L$9</f>
+        <v>9</v>
       </c>
       <c r="F40" s="18">
         <v>2026</v>
@@ -3974,7 +3977,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="41" spans="1:11" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="13" t="s">
         <v>54</v>
       </c>
@@ -3988,8 +3991,8 @@
         <v>55</v>
       </c>
       <c r="E41" s="5">
-        <f>MASTER!E41-MASTER!E41*$L$1</f>
-        <v>27.5</v>
+        <f>MASTER!E41-MASTER!E41*$L$9</f>
+        <v>33</v>
       </c>
       <c r="F41" s="15">
         <v>2026</v>
@@ -4010,7 +4013,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="42" spans="1:11" ht="7.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:12" ht="7.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="21"/>
       <c r="B42" s="21"/>
       <c r="C42" s="21"/>
@@ -4023,7 +4026,7 @@
       <c r="J42" s="22"/>
       <c r="K42" s="22"/>
     </row>
-    <row r="43" spans="1:11" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="13" t="s">
         <v>84</v>
       </c>
@@ -4037,8 +4040,8 @@
         <v>85</v>
       </c>
       <c r="E43" s="5">
-        <f>MASTER!E43-MASTER!E43*$L$1</f>
-        <v>25</v>
+        <f>MASTER!E43-MASTER!E43*$L$9</f>
+        <v>30</v>
       </c>
       <c r="F43" s="15">
         <v>2026</v>
@@ -4059,7 +4062,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="44" spans="1:11" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="14" t="s">
         <v>87</v>
       </c>
@@ -4073,8 +4076,8 @@
         <v>88</v>
       </c>
       <c r="E44" s="5">
-        <f>MASTER!E44-MASTER!E44*$L$1</f>
-        <v>100</v>
+        <f>MASTER!E44-MASTER!E44*$L$9</f>
+        <v>120</v>
       </c>
       <c r="F44" s="18">
         <v>2026</v>
@@ -4095,26 +4098,29 @@
         <v>26</v>
       </c>
     </row>
-    <row r="45" spans="1:11" ht="9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:12" ht="9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="E45" s="3"/>
     </row>
-    <row r="46" spans="1:11" ht="9" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="47" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="27" t="s">
+    <row r="46" spans="1:12" ht="9" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="47" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="28" t="s">
         <v>89</v>
       </c>
-      <c r="B47" s="27"/>
-      <c r="C47" s="27"/>
-      <c r="D47" s="27"/>
-      <c r="E47" s="27"/>
-      <c r="F47" s="27"/>
-      <c r="G47" s="27"/>
-      <c r="H47" s="27"/>
-      <c r="I47" s="27"/>
-      <c r="J47" s="27"/>
-      <c r="K47" s="27"/>
-    </row>
-    <row r="48" spans="1:11" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B47" s="28"/>
+      <c r="C47" s="28"/>
+      <c r="D47" s="28"/>
+      <c r="E47" s="28"/>
+      <c r="F47" s="28"/>
+      <c r="G47" s="28"/>
+      <c r="H47" s="28"/>
+      <c r="I47" s="28"/>
+      <c r="J47" s="28"/>
+      <c r="K47" s="28"/>
+      <c r="L47" s="25">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="13" t="s">
         <v>90</v>
       </c>
@@ -4128,7 +4134,7 @@
         <v>92</v>
       </c>
       <c r="E48" s="5">
-        <f>MASTER!E48-MASTER!E48*$L$1</f>
+        <f>MASTER!E48-MASTER!E48*$L$47</f>
         <v>400</v>
       </c>
       <c r="F48" s="15">
@@ -4164,7 +4170,7 @@
         <v>95</v>
       </c>
       <c r="E49" s="5">
-        <f>MASTER!E49-MASTER!E49*$L$1</f>
+        <f>MASTER!E49-MASTER!E49*$L$47</f>
         <v>450</v>
       </c>
       <c r="F49" s="18">
@@ -4200,7 +4206,7 @@
         <v>98</v>
       </c>
       <c r="E50" s="5">
-        <f>MASTER!E50-MASTER!E50*$L$1</f>
+        <f>MASTER!E50-MASTER!E50*$L$47</f>
         <v>1000</v>
       </c>
       <c r="F50" s="15">
@@ -4236,7 +4242,7 @@
         <v>101</v>
       </c>
       <c r="E51" s="5">
-        <f>MASTER!E51-MASTER!E51*$L$1</f>
+        <f>MASTER!E51-MASTER!E51*$L$47</f>
         <v>700</v>
       </c>
       <c r="F51" s="18">
@@ -4272,7 +4278,7 @@
         <v>103</v>
       </c>
       <c r="E52" s="5">
-        <f>MASTER!E52-MASTER!E52*$L$1</f>
+        <f>MASTER!E52-MASTER!E52*$L$47</f>
         <v>200</v>
       </c>
       <c r="F52" s="15">
@@ -4302,6 +4308,15 @@
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.3">
       <c r="E55" s="3"/>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="E57" s="3"/>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="E58" s="3"/>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="E59" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -4309,7 +4324,7 @@
     <mergeCell ref="A9:K9"/>
     <mergeCell ref="A47:K47"/>
   </mergeCells>
-  <conditionalFormatting sqref="A2:K2 A3 A9 A47 A4:K8 A10:K46 A48:K509">
+  <conditionalFormatting sqref="A2:K2 A3 A4:K8 A9 A47 A48:K509 A10:K46">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>AND($A2&lt;&gt;"",$B2&lt;&gt;"",$J2=0)</formula>
     </cfRule>
@@ -4360,10 +4375,10 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:3" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="28" t="s">
+      <c r="B2" s="29" t="s">
         <v>105</v>
       </c>
-      <c r="C2" s="29"/>
+      <c r="C2" s="30"/>
     </row>
     <row r="4" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="10" t="s">
@@ -4438,10 +4453,10 @@
       </c>
     </row>
     <row r="15" spans="2:3" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="30" t="s">
+      <c r="B15" s="31" t="s">
         <v>124</v>
       </c>
-      <c r="C15" s="29"/>
+      <c r="C15" s="30"/>
     </row>
   </sheetData>
   <mergeCells count="2">
